--- a/BL-B01D1年度证据规划表.xlsx
+++ b/BL-B01D1年度证据规划表.xlsx
@@ -494,7 +494,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>《BL-B01D1 年度证据规划表》v1.0 · 2026-08-17 · 依据手册第35章35.6（上市后证据10类型）编制</t>
+          <t>《BL-B01D1 年度证据规划表》v1.0 · 2026-08-17 · 依据手册第19章19.6（上市后证据10类型）编制</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>依据手册35.6；优先级逻辑：先监管承诺(①②)→注册外证据(③)→真实世界与学术生态(④⑤⑥⑦)→准入与教育(⑧⑨⑩)。</t>
+          <t>依据手册19.6；优先级逻辑：先监管承诺(①②)→注册外证据(③)→真实世界与学术生态(④⑤⑥⑦)→准入与教育(⑧⑨⑩)。</t>
         </is>
       </c>
     </row>
